--- a/cypress/downloads/VisaReport.xlsx
+++ b/cypress/downloads/VisaReport.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
@@ -212,6 +212,15 @@
   </x:si>
   <x:si>
     <x:t>21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -275,8 +284,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:N22" totalsRowShown="0">
-  <x:autoFilter ref="A1:N22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:N25" totalsRowShown="0">
+  <x:autoFilter ref="A1:N25"/>
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="SN"/>
     <x:tableColumn id="2" name="PROCESSING PERSON"/>
@@ -585,7 +594,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:N22"/>
+  <x:dimension ref="A1:N25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:14">
@@ -1469,6 +1478,129 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="N22" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:14">
+      <x:c r="A23" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J23" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K23" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L23" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M23" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="N23" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:14">
+      <x:c r="A24" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J24" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K24" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L24" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M24" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="N24" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:14">
+      <x:c r="A25" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J25" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K25" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L25" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="M25" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="N25" s="0" t="s">
         <x:v>58</x:v>
       </x:c>
     </x:row>

--- a/cypress/downloads/VisaReport.xlsx
+++ b/cypress/downloads/VisaReport.xlsx
@@ -14,48 +14,225 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Email</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VisaTypeName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CurrentStatus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LinkedMembers</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MemberType</x:t>
+    <x:t>PROCESSING PERSON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LAST NAME</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOBILE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMAIL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VISA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXPIRY DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEDICAL CERTIFICATE ISSUE DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>XRAY EXPIRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>POLICE CERTIFICATE DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STATUS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTNER VISA EXPIRY DATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PARTNER VISA</x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>23870</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
+    <x:t>testhshhd...1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Expression of Interest – SMC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/25/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/01/1900 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Active</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/26/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Complaint</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Appeal - IPT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/19/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/15/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/15/2023 06:03:18 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/28/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/27/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02/24/2023 07:48:21 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Critical Purpose Visitor Visa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nimal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>new</x:t>
+  </x:si>
+  <x:si>
+    <x:t>last</x:t>
+  </x:si>
+  <x:si>
+    <x:t>spanish visa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/07/2023 07:48:22 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>first name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>last name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5657</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenz2@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUNAC/IEP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/05/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush1@gmail.con</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06/28/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>st</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Consultation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve"> 2021 RV - Phase 1</x:t>
   </x:si>
   <x:si>
-    <x:t>Approved</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client</x:t>
+    <x:t>06/27/2023 00:00:00 +00:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>211267313</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01/30/2023 14:08:44 +00:00</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -119,17 +296,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:H2" totalsRowShown="0">
-  <x:autoFilter ref="A1:H2"/>
-  <x:tableColumns count="8">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:N14" totalsRowShown="0">
+  <x:autoFilter ref="A1:N14"/>
+  <x:tableColumns count="14">
     <x:tableColumn id="1" name="SN"/>
-    <x:tableColumn id="2" name="Id"/>
-    <x:tableColumn id="3" name="Name"/>
-    <x:tableColumn id="4" name="Email"/>
-    <x:tableColumn id="5" name="VisaTypeName"/>
-    <x:tableColumn id="6" name="CurrentStatus"/>
-    <x:tableColumn id="7" name="LinkedMembers"/>
-    <x:tableColumn id="8" name="MemberType"/>
+    <x:tableColumn id="2" name="PROCESSING PERSON"/>
+    <x:tableColumn id="3" name="FIRST NAME"/>
+    <x:tableColumn id="4" name="LAST NAME"/>
+    <x:tableColumn id="5" name="MOBILE"/>
+    <x:tableColumn id="6" name="EMAIL"/>
+    <x:tableColumn id="7" name="VISA"/>
+    <x:tableColumn id="8" name="EXPIRY DATE"/>
+    <x:tableColumn id="9" name="MEDICAL CERTIFICATE ISSUE DATE"/>
+    <x:tableColumn id="10" name="XRAY EXPIRY"/>
+    <x:tableColumn id="11" name="POLICE CERTIFICATE DATE"/>
+    <x:tableColumn id="12" name="STATUS"/>
+    <x:tableColumn id="13" name="PARTNER VISA EXPIRY DATE"/>
+    <x:tableColumn id="14" name="PARTNER VISA"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -423,10 +606,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H2"/>
+  <x:dimension ref="A1:N14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:8">
+    <x:row r="1" spans="1:14">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -451,25 +634,505 @@
       <x:c r="H1" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8">
+      <x:c r="I1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J1" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K1" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L1" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M1" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N1" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:14">
       <x:c r="A2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="N2" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:14">
+      <x:c r="A3" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K3" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:14">
+      <x:c r="A4" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="K4" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="L4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:14">
+      <x:c r="A5" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J5" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K5" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N5" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:14">
+      <x:c r="A6" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J6" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K6" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N6" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:14">
+      <x:c r="A7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="J7" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="K7" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="L7" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="N7" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:14">
+      <x:c r="A8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:14">
+      <x:c r="A9" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:14">
+      <x:c r="A10" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:14">
+      <x:c r="A11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:14">
+      <x:c r="A12" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:14">
+      <x:c r="A13" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:14">
+      <x:c r="A14" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/VisaReport.xlsx
+++ b/cypress/downloads/VisaReport.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
@@ -74,6 +74,21 @@
   </x:si>
   <x:si>
     <x:t>Child</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush hona1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>khush1@gmail.con</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Preparing</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -137,8 +152,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:H3" totalsRowShown="0">
-  <x:autoFilter ref="A1:H3"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:H4" totalsRowShown="0">
+  <x:autoFilter ref="A1:H4"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="SN"/>
     <x:tableColumn id="2" name="Id"/>
@@ -441,7 +456,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H3"/>
+  <x:dimension ref="A1:H4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -514,6 +529,29 @@
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8">
+      <x:c r="A4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/VisaReport.xlsx
+++ b/cypress/downloads/VisaReport.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
@@ -43,52 +43,103 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>23870</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new last</x:t>
+    <x:t>26947</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">testt </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Appeal - IPT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Preparing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20196</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test school</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Approved</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20923</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
   </x:si>
   <x:si>
     <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve"> 2021 RV - Phase 1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Approved</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24736</x:t>
-  </x:si>
-  <x:si>
-    <x:t>new child</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Assessing</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Child</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25210</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush hona1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>khush1@gmail.con</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Preparing</x:t>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nimal test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24859</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rana44@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mawaz Ejaz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mawazejaz@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Referred Back To INZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20961</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20493</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -152,8 +203,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:H4" totalsRowShown="0">
-  <x:autoFilter ref="A1:H4"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:H10" totalsRowShown="0">
+  <x:autoFilter ref="A1:H10"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="SN"/>
     <x:tableColumn id="2" name="Id"/>
@@ -456,7 +507,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H4"/>
+  <x:dimension ref="A1:H10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -495,63 +546,183 @@
       <x:c r="C2" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="E2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
       <x:c r="A3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="C3" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="E3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:8">
       <x:c r="A4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="H4" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
+      <x:c r="B5" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="C5" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E4" s="0" t="s">
+      <x:c r="D5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:8">
+      <x:c r="A6" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8">
+      <x:c r="A7" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>14</x:v>
+      <x:c r="H7" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8">
+      <x:c r="A8" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8">
+      <x:c r="A9" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:8">
+      <x:c r="A10" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/VisaReport.xlsx
+++ b/cypress/downloads/VisaReport.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
@@ -40,6 +40,9 @@
     <x:t>MemberType</x:t>
   </x:si>
   <x:si>
+    <x:t>ProcessingPersons</x:t>
+  </x:si>
+  <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
@@ -52,21 +55,24 @@
     <x:t>Appeal - IPT</x:t>
   </x:si>
   <x:si>
+    <x:t>Assessing</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20196</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test test</x:t>
+  </x:si>
+  <x:si>
     <x:t>Preparing</x:t>
   </x:si>
   <x:si>
-    <x:t>Client</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20196</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test test</x:t>
-  </x:si>
-  <x:si>
     <x:t>3</x:t>
   </x:si>
   <x:si>
@@ -91,6 +97,9 @@
     <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
   </x:si>
   <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
     <x:t>5</x:t>
   </x:si>
   <x:si>
@@ -112,6 +121,9 @@
     <x:t>rana44@gmail.com</x:t>
   </x:si>
   <x:si>
+    <x:t>Owner nabeel</x:t>
+  </x:si>
+  <x:si>
     <x:t>7</x:t>
   </x:si>
   <x:si>
@@ -130,16 +142,19 @@
     <x:t>8</x:t>
   </x:si>
   <x:si>
+    <x:t>20493</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
     <x:t>20961</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20493</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -203,9 +218,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:H10" totalsRowShown="0">
-  <x:autoFilter ref="A1:H10"/>
-  <x:tableColumns count="8">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:I10" totalsRowShown="0">
+  <x:autoFilter ref="A1:I10"/>
+  <x:tableColumns count="9">
     <x:tableColumn id="1" name="SN"/>
     <x:tableColumn id="2" name="Id"/>
     <x:tableColumn id="3" name="Name"/>
@@ -214,6 +229,7 @@
     <x:tableColumn id="6" name="CurrentStatus"/>
     <x:tableColumn id="7" name="LinkedMembers"/>
     <x:tableColumn id="8" name="MemberType"/>
+    <x:tableColumn id="9" name="ProcessingPersons"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -507,10 +523,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H10"/>
+  <x:dimension ref="A1:I10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:8">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -535,194 +551,212 @@
       <x:c r="H1" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8">
+      <x:c r="I1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
+      <x:c r="A5" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
+      <x:c r="A6" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
+      <x:c r="A7" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8">
-      <x:c r="A5" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="H7" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
+      <x:c r="A8" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
+      <x:c r="A9" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8">
-      <x:c r="A6" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8">
-      <x:c r="A7" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8">
-      <x:c r="A8" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8">
-      <x:c r="A9" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:8">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>44</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/VisaReport.xlsx
+++ b/cypress/downloads/VisaReport.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
@@ -127,6 +127,18 @@
     <x:t>7</x:t>
   </x:si>
   <x:si>
+    <x:t>42132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeel muhammad changes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>test3333@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
     <x:t>20493</x:t>
   </x:si>
   <x:si>
@@ -136,7 +148,7 @@
     <x:t>arsalan team member,Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>8</x:t>
+    <x:t>9</x:t>
   </x:si>
   <x:si>
     <x:t>20961</x:t>
@@ -203,8 +215,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:I9" totalsRowShown="0">
-  <x:autoFilter ref="A1:I9"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:I10" totalsRowShown="0">
+  <x:autoFilter ref="A1:I10"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="SN"/>
     <x:tableColumn id="2" name="Id"/>
@@ -508,7 +520,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I9"/>
+  <x:dimension ref="A1:I10"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -682,17 +694,20 @@
       <x:c r="C8" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -703,19 +718,42 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
+      <x:c r="A10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>39</x:v>
+      <x:c r="H10" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>43</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/VisaReport.xlsx
+++ b/cypress/downloads/VisaReport.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
@@ -139,6 +139,24 @@
     <x:t>8</x:t>
   </x:si>
   <x:si>
+    <x:t>55704</x:t>
+  </x:si>
+  <x:si>
+    <x:t>g masom</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rananabeelahmed968@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agreement Signed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>team member nabeel,Owner nabeel,Nabeel Ahmed,arsalan team member</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
     <x:t>20493</x:t>
   </x:si>
   <x:si>
@@ -148,7 +166,7 @@
     <x:t>arsalan team member,Owner nabeel</x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
+    <x:t>10</x:t>
   </x:si>
   <x:si>
     <x:t>20961</x:t>
@@ -215,8 +233,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:I10" totalsRowShown="0">
-  <x:autoFilter ref="A1:I10"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:I11" totalsRowShown="0">
+  <x:autoFilter ref="A1:I11"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="SN"/>
     <x:tableColumn id="2" name="Id"/>
@@ -520,7 +538,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I10"/>
+  <x:dimension ref="A1:I11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -720,40 +738,66 @@
       <x:c r="C9" s="0" t="s">
         <x:v>42</x:v>
       </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
+      <x:c r="A11" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>43</x:v>
+      <x:c r="H11" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cypress/downloads/VisaReport.xlsx
+++ b/cypress/downloads/VisaReport.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <x:si>
     <x:t>SN</x:t>
   </x:si>
@@ -76,97 +76,58 @@
     <x:t>3</x:t>
   </x:si>
   <x:si>
-    <x:t>28244</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test school</x:t>
+    <x:t>20923</x:t>
+  </x:si>
+  <x:si>
+    <x:t>sufi cup</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>Approved</x:t>
   </x:si>
   <x:si>
+    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+  </x:si>
+  <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
-    <x:t>20923</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sufi cup</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeeloutsourcenzhard@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel,arsalan team member,Nabeel Ahmed</x:t>
+    <x:t>24157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nimal test</x:t>
   </x:si>
   <x:si>
     <x:t>5</x:t>
   </x:si>
   <x:si>
-    <x:t>24157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nimal test</x:t>
+    <x:t>24859</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nbaaa Efgh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rana44@gmail.com</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Owner nabeel</x:t>
   </x:si>
   <x:si>
     <x:t>6</x:t>
   </x:si>
   <x:si>
-    <x:t>24859</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nbaaa Efgh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rana44@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Owner nabeel</x:t>
+    <x:t>20493</x:t>
+  </x:si>
+  <x:si>
+    <x:t>basic web</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arsalan team member,Owner nabeel</x:t>
   </x:si>
   <x:si>
     <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42132</x:t>
-  </x:si>
-  <x:si>
-    <x:t>nabeel muhammad changes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>test3333@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55704</x:t>
-  </x:si>
-  <x:si>
-    <x:t>g masom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>rananabeelahmed968@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Agreement Signed</x:t>
-  </x:si>
-  <x:si>
-    <x:t>team member nabeel,Owner nabeel,Nabeel Ahmed,arsalan team member</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20493</x:t>
-  </x:si>
-  <x:si>
-    <x:t>basic web</x:t>
-  </x:si>
-  <x:si>
-    <x:t>arsalan team member,Owner nabeel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
   </x:si>
   <x:si>
     <x:t>20961</x:t>
@@ -233,8 +194,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:I11" totalsRowShown="0">
-  <x:autoFilter ref="A1:I11"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Grid" displayName="Grid" ref="A1:I8" totalsRowShown="0">
+  <x:autoFilter ref="A1:I8"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="SN"/>
     <x:tableColumn id="2" name="Id"/>
@@ -538,7 +499,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I11"/>
+  <x:dimension ref="A1:I8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -620,40 +581,40 @@
       <x:c r="C4" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>14</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -666,54 +627,54 @@
       <x:c r="C6" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>14</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>12</x:v>
@@ -725,79 +686,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>35</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:9">
-      <x:c r="A9" s="0" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:9">
-      <x:c r="A10" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:9">
-      <x:c r="A11" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
